--- a/results/kxcpi_benchmarks.xlsx
+++ b/results/kxcpi_benchmarks.xlsx
@@ -3576,7 +3576,7 @@
         <v>-0.1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-0.081</v>
+        <v>-0.082</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>0.121</v>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>0.221</v>
@@ -3629,7 +3629,7 @@
         <v>-0.1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-0.056</v>
+        <v>-0.057</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>0.245</v>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="n">
-        <v>0.044</v>
+        <v>0.043</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>0.345</v>
@@ -4159,7 +4159,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.392</v>
+        <v>0.393</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>0.268</v>
@@ -4172,7 +4172,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="n">
-        <v>0.392</v>
+        <v>0.393</v>
       </c>
       <c r="M34" s="2" t="n">
         <v>0.268</v>
@@ -4636,7 +4636,7 @@
         <v>1.2</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>1.051</v>
+        <v>1.05</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>1.112</v>
@@ -4649,7 +4649,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="n">
-        <v>0.149</v>
+        <v>0.15</v>
       </c>
       <c r="M43" s="2" t="n">
         <v>0.08799999999999999</v>
@@ -4742,7 +4742,7 @@
         <v>1</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.805</v>
+        <v>0.804</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>0.672</v>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="n">
-        <v>0.195</v>
+        <v>0.196</v>
       </c>
       <c r="M45" s="2" t="n">
         <v>0.328</v>
@@ -4795,7 +4795,7 @@
         <v>1</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.778</v>
+        <v>0.777</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>0.672</v>
@@ -4808,7 +4808,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="n">
-        <v>0.222</v>
+        <v>0.223</v>
       </c>
       <c r="M46" s="2" t="n">
         <v>0.328</v>
@@ -8399,7 +8399,7 @@
         <v>0.2</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.161</v>
+        <v>0.162</v>
       </c>
       <c r="H114" s="2" t="n">
         <v>0.205</v>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="n">
-        <v>0.039</v>
+        <v>0.038</v>
       </c>
       <c r="M114" s="2" t="n">
         <v>0.005</v>
@@ -8770,7 +8770,7 @@
         <v>0.3</v>
       </c>
       <c r="G121" s="2" t="n">
-        <v>0.163</v>
+        <v>0.164</v>
       </c>
       <c r="H121" s="2" t="n">
         <v>0.131</v>
@@ -8783,7 +8783,7 @@
       </c>
       <c r="K121" s="2" t="inlineStr"/>
       <c r="L121" s="2" t="n">
-        <v>0.137</v>
+        <v>0.136</v>
       </c>
       <c r="M121" s="2" t="n">
         <v>0.169</v>
@@ -10307,7 +10307,7 @@
         <v>0.4</v>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0.382</v>
+        <v>0.383</v>
       </c>
       <c r="H150" s="2" t="n">
         <v>0.377</v>
@@ -10320,7 +10320,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="M150" s="2" t="n">
         <v>0.023</v>
@@ -10360,7 +10360,7 @@
         <v>0.4</v>
       </c>
       <c r="G151" s="2" t="n">
-        <v>0.387</v>
+        <v>0.388</v>
       </c>
       <c r="H151" s="2" t="n">
         <v>0.377</v>
@@ -10373,7 +10373,7 @@
       </c>
       <c r="K151" s="2" t="inlineStr"/>
       <c r="L151" s="2" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="M151" s="2" t="n">
         <v>0.023</v>
@@ -10943,7 +10943,7 @@
         <v>0.4</v>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0.332</v>
+        <v>0.333</v>
       </c>
       <c r="H162" s="2" t="n">
         <v>0.305</v>
@@ -10956,7 +10956,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr"/>
       <c r="L162" s="2" t="n">
-        <v>0.068</v>
+        <v>0.067</v>
       </c>
       <c r="M162" s="2" t="n">
         <v>0.095</v>
@@ -13169,7 +13169,7 @@
         <v>0.6</v>
       </c>
       <c r="G204" s="2" t="n">
-        <v>0.59</v>
+        <v>0.591</v>
       </c>
       <c r="H204" s="2" t="n">
         <v>0.448</v>
@@ -13182,7 +13182,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr"/>
       <c r="L204" s="2" t="n">
-        <v>0.01</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="M204" s="2" t="n">
         <v>0.152</v>
@@ -13593,7 +13593,7 @@
         <v>0.2</v>
       </c>
       <c r="G212" s="2" t="n">
-        <v>0.223</v>
+        <v>0.224</v>
       </c>
       <c r="H212" s="2" t="n">
         <v>0.135</v>
@@ -13606,7 +13606,7 @@
       </c>
       <c r="K212" s="2" t="inlineStr"/>
       <c r="L212" s="2" t="n">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="M212" s="2" t="n">
         <v>0.065</v>
@@ -14123,7 +14123,7 @@
         <v>0.9</v>
       </c>
       <c r="G222" s="2" t="n">
-        <v>0.866</v>
+        <v>0.867</v>
       </c>
       <c r="H222" s="2" t="n">
         <v>0.844</v>
@@ -14136,7 +14136,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr"/>
       <c r="L222" s="2" t="n">
-        <v>0.034</v>
+        <v>0.033</v>
       </c>
       <c r="M222" s="2" t="n">
         <v>0.056</v>
@@ -14176,7 +14176,7 @@
         <v>0.9</v>
       </c>
       <c r="G223" s="2" t="n">
-        <v>0.675</v>
+        <v>0.674</v>
       </c>
       <c r="H223" s="2" t="n">
         <v>0.466</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="K223" s="2" t="inlineStr"/>
       <c r="L223" s="2" t="n">
-        <v>0.225</v>
+        <v>0.226</v>
       </c>
       <c r="M223" s="2" t="n">
         <v>0.434</v>

--- a/results/kxcpi_benchmarks.xlsx
+++ b/results/kxcpi_benchmarks.xlsx
@@ -4677,7 +4677,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>2022-03-14</t>
+          <t>2022-03-13</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -4689,10 +4689,10 @@
         <v>1.2</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.998</v>
+        <v>1.008</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>1.098</v>
+        <v>1.004</v>
       </c>
       <c r="I44" s="2" t="n">
         <v>0.8</v>
@@ -4702,10 +4702,10 @@
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="n">
-        <v>0.202</v>
+        <v>0.192</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.102</v>
+        <v>0.196</v>
       </c>
       <c r="N44" s="2" t="n">
         <v>0.4</v>
@@ -6226,7 +6226,7 @@
         <v>0.4</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.407</v>
+        <v>0.406</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>0.537</v>
@@ -6239,7 +6239,7 @@
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="M73" s="2" t="n">
         <v>0.137</v>
@@ -7233,7 +7233,7 @@
         <v>0.1</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>0.297</v>
+        <v>0.293</v>
       </c>
       <c r="H92" s="2" t="n">
         <v>0.274</v>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="n">
-        <v>0.197</v>
+        <v>0.193</v>
       </c>
       <c r="M92" s="2" t="n">
         <v>0.174</v>
@@ -8558,7 +8558,7 @@
         <v>0.4</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.452</v>
+        <v>0.449</v>
       </c>
       <c r="H117" s="2" t="n">
         <v>0.434</v>
@@ -8571,7 +8571,7 @@
       </c>
       <c r="K117" s="2" t="inlineStr"/>
       <c r="L117" s="2" t="n">
-        <v>0.052</v>
+        <v>0.049</v>
       </c>
       <c r="M117" s="2" t="n">
         <v>0.034</v>
@@ -9565,7 +9565,7 @@
         <v>0.4</v>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.233</v>
+        <v>0.224</v>
       </c>
       <c r="H136" s="2" t="n">
         <v>0.245</v>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr"/>
       <c r="L136" s="2" t="n">
-        <v>0.167</v>
+        <v>0.176</v>
       </c>
       <c r="M136" s="2" t="n">
         <v>0.155</v>
